--- a/out/MLP-S4_repeat_5_000008.xlsx
+++ b/out/MLP-S4_repeat_5_000008.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.990389075499146</v>
+        <v>1.180723568071307</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>2.590389075499146</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>2.590389075499146</v>
+        <v>-1.023677129033441</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>2.590389075499146</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.5557497644722087</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.5557497644722087</v>
+        <v>1.180723568071307</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.155749764472209</v>
+        <v>1.180723568071307</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.023677129033441</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.155749764472209</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.155749764472209</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>2.590389075499146</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.5557497644722087</v>
+        <v>-1.023677129033441</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.5557497644722087</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.155749764472209</v>
+        <v>1.180723568071307</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.023677129033441</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>2.590389075499146</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.5557497644722087</v>
+        <v>-1.023677129033441</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.5557497644722087</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.023677129033441</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.155749764472209</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>2.590389075499146</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>2.590389075499146</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>2.590389075499146</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>2.590389075499146</v>
+        <v>-1.023677129033441</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>2.590389075499146</v>
+        <v>1.180723568071307</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>2.590389075499146</v>
+        <v>1.180723568071307</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>2.590389075499146</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>2.590389075499146</v>
+        <v>1.180723568071307</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.990389075499146</v>
+        <v>1.180723568071307</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.990389075499146</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.590389075499146</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.590389075499146</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.590389075499146</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.590389075499146</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.000159085565471556</v>
+        <v>-0.0001406177009765524</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1827587595276246</v>
+        <v>-0.1615427303031176</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>2.590389075499146</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1829178450930962</v>
+        <v>-0.1616833480040942</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>2.590389075499146</v>
+        <v>1.180723568071307</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1829178450930962</v>
+        <v>-0.1616833480040942</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1829178450930962</v>
+        <v>-0.1616833480040942</v>
       </c>
     </row>
     <row r="49">
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1829178450930962</v>
+        <v>-0.1616833480040942</v>
       </c>
     </row>
     <row r="50">
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1829178450930962</v>
+        <v>-0.1616833480040942</v>
       </c>
     </row>
     <row r="51">
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.155749764472209</v>
+        <v>1.180723568071307</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1829178450930962</v>
+        <v>-0.1616833480040942</v>
       </c>
     </row>
     <row r="52">
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1829178450930962</v>
+        <v>-0.1616833480040942</v>
       </c>
     </row>
     <row r="53">
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.990389075499146</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1829178450930962</v>
+        <v>-0.1616833480040942</v>
       </c>
     </row>
     <row r="54">
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.155749764472209</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1829178450930962</v>
+        <v>-0.1616833480040942</v>
       </c>
     </row>
     <row r="55">
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.5557497644722087</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1829178450930962</v>
+        <v>-0.1616833480040942</v>
       </c>
     </row>
     <row r="56">
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.155749764472209</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1829178450930962</v>
+        <v>-0.1616833480040942</v>
       </c>
     </row>
     <row r="57">
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.155749764472209</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1829178450930962</v>
+        <v>-0.1616833480040942</v>
       </c>
     </row>
     <row r="58">
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>2.590389075499146</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1829178450930962</v>
+        <v>-0.1616833480040942</v>
       </c>
     </row>
     <row r="59">
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>2.590389075499146</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1830529433513669</v>
+        <v>-0.161804835695005</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.4857823126353057</v>
+        <v>0.4368418120883298</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.5557497644722087</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.7894449162271289</v>
+        <v>0.7127180552363491</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.03461192436865792</v>
+        <v>0.03112488739376818</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.5557497644722087</v>
+        <v>1.180723568071307</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.3721066898628245</v>
+        <v>0.337424834738658</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.06069752232921957</v>
+        <v>0.0545825759020717</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>1.990389075499146</v>
+        <v>1.180723568071307</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.458878259349715</v>
+        <v>0.4154546388544033</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.07374000952296683</v>
+        <v>0.06631138356995801</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.5557497644722087</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.545655604813698</v>
+        <v>0.4934896365311984</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01951345409026527</v>
+        <v>0.01754748852435274</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.5557497644722087</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.5108480630156214</v>
+        <v>0.462188898311944</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.01084122068196866</v>
+        <v>0.009748307293672601</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.990389075499146</v>
+        <v>1.180723568071307</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.5129978243995577</v>
+        <v>0.4641215731132007</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.02277769162908367</v>
+        <v>0.0204832806673934</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>2.590389075499146</v>
+        <v>1.180723568071307</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.5477262725634361</v>
+        <v>0.4953518032202523</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.008946045157308449</v>
+        <v>0.00804379530719415</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>2.590389075499146</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.5428203044645052</v>
+        <v>0.4909395134815944</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.006368635324465501</v>
+        <v>0.005726959454181017</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.5557497644722087</v>
+        <v>-1.023677129033441</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.5466095263994253</v>
+        <v>0.4943467978864345</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.002504382935466659</v>
+        <v>0.002251815172481378</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.155749764472209</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.5452429702002283</v>
+        <v>0.4931172814345592</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001419265766316749</v>
+        <v>0.001275914341784869</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.5455756565603237</v>
+        <v>0.4934159798817881</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0005375585845749554</v>
+        <v>0.0004823632307329145</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.5452303693773439</v>
+        <v>0.4931049431740632</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0002493218624291358</v>
+        <v>0.0002239997722305638</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.5451910685849956</v>
+        <v>0.4930690576121218</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>8.784240885070706e-05</v>
+        <v>7.896183061281334e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.5451180260966455</v>
+        <v>0.49300278940305</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>2.266517359622213e-05</v>
+        <v>1.980325908626812e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.5450746174819442</v>
+        <v>0.4929633540933177</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>8.832586798111064e-06</v>
+        <v>7.401629543134059e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.5450695958873247</v>
+        <v>0.4929583347326247</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>2.191662034084867e-06</v>
+        <v>1.677971888793091e-06</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.155749764472209</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.5450656505512246</v>
+        <v>0.4929542799397891</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-1.195152058104458e-07</v>
+        <v>-8.167273192660964e-07</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.023677129033441</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.5450633996234929</v>
+        <v>0.4929516625363703</v>
       </c>
     </row>
     <row r="78">
@@ -62943,7 +62943,7 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>-2.504786695239595e-06</v>
+        <v>-3.128590021429696e-06</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.023677129033441</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.5450578079634847</v>
+        <v>0.4929461452943806</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.5450514839694768</v>
+        <v>0.4929398213003727</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.155749764472209</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.5450461161808984</v>
+        <v>0.4929344535117943</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.023677129033441</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.5450461529293901</v>
+        <v>0.492934490260286</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.155749764472209</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.5450462631748656</v>
+        <v>0.4929346005057615</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.155749764472209</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.5450463366718492</v>
+        <v>0.4929346740027452</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.155749764472209</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.5450465204143085</v>
+        <v>0.4929348577452043</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>2.590389075499146</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.5450480638509649</v>
+        <v>0.4929364011818608</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.5557497644722087</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.5450495337906379</v>
+        <v>0.4929378711215339</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.5557497644722087</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.54505078323936</v>
+        <v>0.4929391205702559</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>2.590389075499146</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.5450521429335573</v>
+        <v>0.4929404802644532</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>2.590389075499146</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.545049938024048</v>
+        <v>0.4929382753549439</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.5557497644722087</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.5450495337906379</v>
+        <v>0.4929378711215339</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.5557497644722087</v>
+        <v>1.180723568071307</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.545048688575326</v>
+        <v>0.492937025906222</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.5450492398027033</v>
+        <v>0.4929375771335992</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.5450489090662769</v>
+        <v>0.4929372463971728</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.5450486150783423</v>
+        <v>0.4929369524092383</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.545048688575326</v>
+        <v>0.492937025906222</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.5450482475934241</v>
+        <v>0.49293658492432</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.5450481373479485</v>
+        <v>0.4929364746788444</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.5450481005994569</v>
+        <v>0.4929364379303527</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.5450482475934241</v>
+        <v>0.49293658492432</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>2.590389075499146</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.5450477698630304</v>
+        <v>0.4929361071939263</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>2.590389075499146</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.5450487253238177</v>
+        <v>0.4929370626547137</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.5557497644722087</v>
+        <v>-1.023677129033441</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.545048688575326</v>
+        <v>0.492937025906222</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.5557497644722087</v>
+        <v>-1.023677129033441</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.5450483578388996</v>
+        <v>0.4929366951697955</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.5450487988208016</v>
+        <v>0.4929371361516975</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.5450481740964405</v>
+        <v>0.4929365114273364</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.5450479903539812</v>
+        <v>0.4929363276848772</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.5450475861205712</v>
+        <v>0.4929359234514672</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.5450467409052593</v>
+        <v>0.4929350782361552</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.155749764472209</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.5450467041567676</v>
+        <v>0.4929350414876635</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.023677129033441</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.5450468511507348</v>
+        <v>0.4929351884816308</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.155749764472209</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.5450467776537512</v>
+        <v>0.4929351149846471</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.155749764472209</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.5450468511507348</v>
+        <v>0.4929351884816308</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.023677129033441</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.5450468878992267</v>
+        <v>0.4929352252301227</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.155749764472209</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.5450467776537512</v>
+        <v>0.4929351149846471</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.5450472186356532</v>
+        <v>0.4929355559665491</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.155749764472209</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.5450471083901776</v>
+        <v>0.4929354457210736</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.155749764472209</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.5450470716416856</v>
+        <v>0.4929354089725816</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.023677129033441</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.545046998144702</v>
+        <v>0.492935335475598</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.5450469613962103</v>
+        <v>0.4929352987271063</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.5450467409052593</v>
+        <v>0.4929350782361552</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.5450466674082757</v>
+        <v>0.4929350047391716</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.5450465939112921</v>
+        <v>0.492934931242188</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.155749764472209</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.545046630659784</v>
+        <v>0.4929349679906799</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.155749764472209</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.5450465204143085</v>
+        <v>0.4929348577452043</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.155749764472209</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.545046630659784</v>
+        <v>0.4929349679906799</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.155749764472209</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.5450469246477184</v>
+        <v>0.4929352619786144</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-S4_repeat_5_000008.xlsx
+++ b/out/MLP-S4_repeat_5_000008.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.155749764472209</v>
+        <v>0.4518763352092359</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.990389075499146</v>
+        <v>0.8114350597773907</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>2.590389075499146</v>
+        <v>1.7305525089137</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>2.590389075499146</v>
+        <v>1.7305525089137</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>2.590389075499146</v>
+        <v>1.011435059777391</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.5557497644722087</v>
+        <v>0.292317610641081</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.5557497644722087</v>
+        <v>-0.4267998384952287</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA15" t="n">
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.155749764472209</v>
+        <v>0.09231761064108085</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>2.590389075499146</v>
+        <v>0.2923176106410809</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.5557497644722087</v>
+        <v>0.2923176106410809</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.5557497644722087</v>
+        <v>-0.4267998384952287</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.4267998384952287</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA24" t="n">
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.155749764472209</v>
+        <v>0.09231761064108085</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>2.590389075499146</v>
+        <v>0.2923176106410809</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.5557497644722087</v>
+        <v>0.2923176106410809</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.5557497644722087</v>
+        <v>-0.4267998384952287</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.4267998384952287</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA29" t="n">
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.155749764472209</v>
+        <v>0.09231761064108085</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>2.590389075499146</v>
+        <v>1.011435059777391</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>2.590389075499146</v>
+        <v>1.7305525089137</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>2.590389075499146</v>
+        <v>1.7305525089137</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>2.590389075499146</v>
+        <v>1.7305525089137</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>2.590389075499146</v>
+        <v>1.7305525089137</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>2.590389075499146</v>
+        <v>1.7305525089137</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>2.590389075499146</v>
+        <v>1.7305525089137</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>2.590389075499146</v>
+        <v>1.011435059777391</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.155749764472209</v>
+        <v>0.09231761064108085</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA39" t="n">
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.155749764472209</v>
+        <v>0.09231761064108085</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.990389075499146</v>
+        <v>0.8114350597773905</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.990389075499146</v>
+        <v>1.5305525089137</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.590389075499146</v>
+        <v>1.7305525089137</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.590389075499146</v>
+        <v>1.7305525089137</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.590389075499146</v>
+        <v>1.7305525089137</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.590389075499146</v>
+        <v>1.7305525089137</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.000159085565471556</v>
+        <v>-0.000139473034625873</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1827587595276246</v>
+        <v>-0.1602277285194828</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>2.590389075499146</v>
+        <v>1.7305525089137</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1829178450930962</v>
+        <v>-0.1603672015541086</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>2.590389075499146</v>
+        <v>1.011435059777391</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1829178450930962</v>
+        <v>-0.1603672015541086</v>
       </c>
     </row>
     <row r="48">
@@ -39097,17 +39097,17 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA48" t="n">
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.155749764472209</v>
+        <v>0.09231761064108085</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1829178450930962</v>
+        <v>-0.1603672015541086</v>
       </c>
     </row>
     <row r="49">
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1829178450930962</v>
+        <v>-0.1603672015541086</v>
       </c>
     </row>
     <row r="50">
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1829178450930962</v>
+        <v>-0.1603672015541086</v>
       </c>
     </row>
     <row r="51">
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1829178450930962</v>
+        <v>-0.1603672015541086</v>
       </c>
     </row>
     <row r="52">
@@ -42277,17 +42277,17 @@
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA52" t="n">
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.155749764472209</v>
+        <v>0.09231761064108085</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1829178450930962</v>
+        <v>-0.1603672015541086</v>
       </c>
     </row>
     <row r="53">
@@ -43072,17 +43072,17 @@
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA53" t="n">
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.990389075499146</v>
+        <v>0.09231761064108088</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1829178450930962</v>
+        <v>-0.1603672015541086</v>
       </c>
     </row>
     <row r="54">
@@ -43867,17 +43867,17 @@
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA54" t="n">
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.155749764472209</v>
+        <v>0.09231761064108088</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1829178450930962</v>
+        <v>-0.1603672015541086</v>
       </c>
     </row>
     <row r="55">
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.5557497644722087</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1829178450930962</v>
+        <v>-0.1603672015541086</v>
       </c>
     </row>
     <row r="56">
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1829178450930962</v>
+        <v>-0.1603672015541086</v>
       </c>
     </row>
     <row r="57">
@@ -46252,17 +46252,17 @@
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA57" t="n">
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.155749764472209</v>
+        <v>0.09231761064108085</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1829178450930962</v>
+        <v>-0.1603672015541086</v>
       </c>
     </row>
     <row r="58">
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>2.590389075499146</v>
+        <v>1.011435059777391</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1829178450930962</v>
+        <v>-0.1603672015541086</v>
       </c>
     </row>
     <row r="59">
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>2.590389075499146</v>
+        <v>1.011435059777391</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1830529433513669</v>
+        <v>-0.1604725866653029</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.4857823126353057</v>
+        <v>0.3789408593852645</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.5557497644722087</v>
+        <v>0.2923176106410809</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.7894449162271289</v>
+        <v>0.5981367124315847</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.03461192436865792</v>
+        <v>0.02699942008405706</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.5557497644722087</v>
+        <v>0.2923176106410809</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.3721066898628245</v>
+        <v>0.2725869038176264</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.06069752232921957</v>
+        <v>0.04734791187465329</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>1.990389075499146</v>
+        <v>0.09231761064108079</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.458878259349715</v>
+        <v>0.3402742239524855</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.07374000952296683</v>
+        <v>0.05752212118368595</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.5557497644722087</v>
+        <v>0.2923176106410809</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.545655604813698</v>
+        <v>0.4079660492662743</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01951345409026527</v>
+        <v>0.01522179449329925</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.5557497644722087</v>
+        <v>0.2923176106410809</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.5108480630156214</v>
+        <v>0.3808140765508113</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.01084122068196866</v>
+        <v>0.008455448354311976</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.990389075499146</v>
+        <v>1.011435059777391</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.5129978243995577</v>
+        <v>0.3824899058941803</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.02277769162908367</v>
+        <v>0.01776820201427167</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>2.590389075499146</v>
+        <v>1.7305525089137</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.5477262725634361</v>
+        <v>0.4095805388110846</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.008946045157308449</v>
+        <v>0.006976839444173076</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>2.590389075499146</v>
+        <v>1.011435059777391</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.5428203044645052</v>
+        <v>0.4057524396955031</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.006368635324465501</v>
+        <v>0.004967987994704746</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.5557497644722087</v>
+        <v>0.2923176106410809</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.5466095263994253</v>
+        <v>0.4087074555536215</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.002504382935466659</v>
+        <v>0.001951721217536502</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.5452429702002283</v>
+        <v>0.4076403984133771</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001419265766316749</v>
+        <v>0.001106358893413828</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.5455756565603237</v>
+        <v>0.4078988961034515</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0005375585845749554</v>
+        <v>0.0004177729230454198</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.5452303693773439</v>
+        <v>0.4076283697746529</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0002493218624291358</v>
+        <v>0.000193172879814911</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.5451910685849956</v>
+        <v>0.4075965683875277</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>8.784240885070706e-05</v>
+        <v>6.76592764918577e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.5451180260966455</v>
+        <v>0.4075382538340504</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>2.266517359622213e-05</v>
+        <v>1.64643588246551e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.5450746174819442</v>
+        <v>0.4075031233103557</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>8.832586798111064e-06</v>
+        <v>5.970672288157051e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.5450695958873247</v>
+        <v>0.4074981061835887</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>2.191662034084867e-06</v>
+        <v>6.505915982095382e-07</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.5450656505512246</v>
+        <v>0.407493942722758</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-1.195152058104458e-07</v>
+        <v>-8.167273192660964e-07</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.5450633996234929</v>
+        <v>0.4074911415768804</v>
       </c>
     </row>
     <row r="78">
@@ -62943,7 +62943,7 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>-2.504786695239595e-06</v>
+        <v>-3.128590021429696e-06</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.5450578079634847</v>
+        <v>0.407485697831874</v>
       </c>
     </row>
     <row r="79">
@@ -63738,7 +63738,7 @@
         <v>0</v>
       </c>
       <c r="IY79" t="n">
-        <v>-4.413072433009741e-06</v>
+        <v>-4.70653621650487e-06</v>
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.5450514839694768</v>
+        <v>0.4074797050984437</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.5450461161808984</v>
+        <v>0.4074743373098653</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.5450461529293901</v>
+        <v>0.407474374058357</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.5450462631748656</v>
+        <v>0.4074744843038325</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.5450463366718492</v>
+        <v>0.4074745578008162</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.155749764472209</v>
+        <v>0.2923176106410809</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.5450465204143085</v>
+        <v>0.4074747415432753</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>2.590389075499146</v>
+        <v>0.2923176106410809</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.5450480638509649</v>
+        <v>0.4074762849799318</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.5557497644722087</v>
+        <v>0.2923176106410809</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.5450495337906379</v>
+        <v>0.4074777549196049</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.5557497644722087</v>
+        <v>0.2923176106410809</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.54505078323936</v>
+        <v>0.4074790043683268</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>2.590389075499146</v>
+        <v>1.011435059777391</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.5450521429335573</v>
+        <v>0.4074803640625242</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>2.590389075499146</v>
+        <v>1.011435059777391</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.545049938024048</v>
+        <v>0.4074781591530149</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.5557497644722087</v>
+        <v>0.2923176106410809</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.5450495337906379</v>
+        <v>0.4074777549196049</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.5557497644722087</v>
+        <v>-0.4267998384952287</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.545048688575326</v>
+        <v>0.4074769097042929</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.5450492398027033</v>
+        <v>0.4074774609316701</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.5450489090662769</v>
+        <v>0.4074771301952437</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.5450486150783423</v>
+        <v>0.4074768362073093</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.545048688575326</v>
+        <v>0.4074769097042929</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.5450482475934241</v>
+        <v>0.407476468722391</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.5450481373479485</v>
+        <v>0.4074763584769154</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.5450481005994569</v>
+        <v>0.4074763217284237</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.155749764472209</v>
+        <v>0.2923176106410809</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.5450482475934241</v>
+        <v>0.407476468722391</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>2.590389075499146</v>
+        <v>1.011435059777391</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.5450477698630304</v>
+        <v>0.4074759909919973</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>2.590389075499146</v>
+        <v>1.011435059777391</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.5450487253238177</v>
+        <v>0.4074769464527846</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.5557497644722087</v>
+        <v>0.2923176106410809</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.545048688575326</v>
+        <v>0.4074769097042929</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.5557497644722087</v>
+        <v>-0.4267998384952287</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.5450483578388996</v>
+        <v>0.4074765789678665</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.5450487988208016</v>
+        <v>0.4074770199497684</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.5450481740964405</v>
+        <v>0.4074763952254073</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.5450479903539812</v>
+        <v>0.4074762114829482</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.5450475861205712</v>
+        <v>0.4074758072495381</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.5450467409052593</v>
+        <v>0.4074749620342262</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.5450467041567676</v>
+        <v>0.4074749252857345</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.5450468511507348</v>
+        <v>0.4074750722797017</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.5450467776537512</v>
+        <v>0.4074749987827181</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.5450468511507348</v>
+        <v>0.4074750722797017</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.5450468878992267</v>
+        <v>0.4074751090281936</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.5450467776537512</v>
+        <v>0.4074749987827181</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.5450472186356532</v>
+        <v>0.40747543976462</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.5450471083901776</v>
+        <v>0.4074753295191445</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.5450470716416856</v>
+        <v>0.4074752927706526</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.545046998144702</v>
+        <v>0.4074752192736689</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.5450469613962103</v>
+        <v>0.4074751825251772</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.5450467409052593</v>
+        <v>0.4074749620342262</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.5450466674082757</v>
+        <v>0.4074748885372426</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.5450465939112921</v>
+        <v>0.4074748150402589</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.545046630659784</v>
+        <v>0.4074748517887509</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.5450465204143085</v>
+        <v>0.4074747415432753</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.545046630659784</v>
+        <v>0.4074748517887509</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.5450469246477184</v>
+        <v>0.4074751457766853</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-S4_repeat_5_000008.xlsx
+++ b/out/MLP-S4_repeat_5_000008.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>0.4468014538288116</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.4518763352092359</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.5186964273452759</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.8114350597773907</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.603836715221405</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.7305525089137</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.6530689001083374</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.7305525089137</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0.5306127667427063</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.011435059777391</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>0.4616235792636871</v>
       </c>
       <c r="JB7" t="n">
-        <v>0.292317610641081</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>0.4746067523956299</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.4267998384952287</v>
+        <v>0.16</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>0.4208788573741913</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>0.4432602822780609</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>0.4352643489837646</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>0.4712470173835754</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.3</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>0.456270694732666</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>0.4661141633987427</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.6267998384952288</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>0.4708754122257233</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.09231761064108085</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.5507197976112366</v>
       </c>
       <c r="JB16" t="n">
-        <v>0.2923176106410809</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>0.4853815734386444</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.2923176106410809</v>
+        <v>0.16</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>0.4485243856906891</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.4267998384952287</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>0.4490446150302887</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.4267998384952287</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>0.4518507719039917</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>0.4482607245445251</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>0.4425079524517059</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>0.4655213952064514</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>0.46238112449646</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.09231761064108085</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.5018675327301025</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.2923176106410809</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>0.4800081551074982</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.2923176106410809</v>
+        <v>0.3</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>0.4777425527572632</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.4267998384952287</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>0.4753337800502777</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.4267998384952287</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>0.4860984086990356</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.09231761064108085</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.5079076886177063</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.011435059777391</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.5401238203048706</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.7305525089137</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.6924175620079041</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.7305525089137</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0.5591307282447815</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.7305525089137</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.5486937761306763</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.7305525089137</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.5362213253974915</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.7305525089137</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.503720760345459</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.7305525089137</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.5498989224433899</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.011435059777391</v>
+        <v>-0.16</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>0.4984896779060364</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.09231761064108085</v>
+        <v>-0.16</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>0.4946294128894806</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.09231761064108085</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.575122594833374</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.8114350597773905</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.592607855796814</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.5305525089137</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.5866009593009949</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.7305525089137</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.64347904920578</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.7305525089137</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.7032928466796875</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.7305525089137</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.7069377303123474</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.7305525089137</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.000139473034625873</v>
+        <v>-0.0001196160965063609</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1602277285194828</v>
+        <v>-0.1374159204966616</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.5525102019309998</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.7305525089137</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1603672015541086</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.6042790412902832</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.011435059777391</v>
+        <v>-0.3</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1603672015541086</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="48">
@@ -39097,17 +39097,17 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>0.4728132784366608</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.09231761064108085</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1603672015541086</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="49">
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>0.496065229177475</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1603672015541086</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="50">
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>0.4508097469806671</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1603672015541086</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="51">
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>0.4481391906738281</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1603672015541086</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="52">
@@ -42277,17 +42277,17 @@
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>0.4455313980579376</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.09231761064108085</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1603672015541086</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="53">
@@ -43072,17 +43072,17 @@
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.5142900943756104</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.09231761064108088</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1603672015541086</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="54">
@@ -43867,17 +43867,17 @@
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>0.4793246388435364</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.09231761064108088</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1603672015541086</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="55">
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>0.4933176338672638</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1603672015541086</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="56">
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>0.4897562563419342</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1603672015541086</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="57">
@@ -46252,17 +46252,17 @@
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>0.494876503944397</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.09231761064108085</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1603672015541086</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="58">
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.5284181237220764</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.011435059777391</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1603672015541086</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="59">
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.5957682132720947</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.011435059777391</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1604725866653029</v>
+        <v>-0.1376191723436012</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.3789408593852645</v>
+        <v>0.3007348545556521</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>0.4833327531814575</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.2923176106410809</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.5981367124315847</v>
+        <v>0.4644284731798686</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.02699942008405706</v>
+        <v>0.02142733183229223</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>0.4981625378131866</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.2923176106410809</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.2725869038176264</v>
+        <v>0.2060653562563302</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.04734791187465329</v>
+        <v>0.03757611096979401</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.5404269099235535</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.09231761064108079</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.3402742239524855</v>
+        <v>0.2597833525048359</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.05752212118368595</v>
+        <v>0.04565053712481063</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>0.4516985714435577</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.2923176106410809</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.4079660492662743</v>
+        <v>0.3135051078826909</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01522179449329925</v>
+        <v>0.01208027590643986</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>0.3787816762924194</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.2923176106410809</v>
+        <v>0.3</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.3808140765508113</v>
+        <v>0.2919565449340034</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.008455448354311976</v>
+        <v>0.006709501790061913</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.5800488591194153</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.011435059777391</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.3824899058941803</v>
+        <v>0.2932855162938063</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.01776820201427167</v>
+        <v>0.01410047189130365</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.581619918346405</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.7305525089137</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.4095805388110846</v>
+        <v>0.3147854440076307</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.006976839444173076</v>
+        <v>0.005536872904863139</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.5125868320465088</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.011435059777391</v>
+        <v>0.16</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.4057524396955031</v>
+        <v>0.3117461008848182</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.004967987994704746</v>
+        <v>0.003941651589276608</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>0.4337862133979797</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.2923176106410809</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.4087074555536215</v>
+        <v>0.3140902220375668</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.001951721217536502</v>
+        <v>0.00154842753147936</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>0.4624049365520477</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.4076403984133771</v>
+        <v>0.3132423539142546</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001106358893413828</v>
+        <v>0.0008766883315294164</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>0.4015043675899506</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.4078988961034515</v>
+        <v>0.3134463978514564</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0004177729230454198</v>
+        <v>0.0003308695999749724</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>0.3819380700588226</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.4076283697746529</v>
+        <v>0.3132307438810405</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.000193172879814911</v>
+        <v>0.0001524373434085126</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>0.3300550282001495</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.4075965683875277</v>
+        <v>0.3132045100572058</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>6.76592764918577e-05</v>
+        <v>5.232009589913218e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>0.3383125960826874</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.4075382538340504</v>
+        <v>0.3131573887342317</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>1.64643588246551e-05</v>
+        <v>1.217148705972408e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>0.3573591113090515</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.4075031233103557</v>
+        <v>0.3131285489044171</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>5.970672288157051e-06</v>
+        <v>3.58574352986204e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>0.3487291932106018</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.4074981061835887</v>
+        <v>0.3131235355008605</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>6.505915982095382e-07</v>
+        <v>-3.767886923740136e-07</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>0.3838661313056946</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.407493942722758</v>
+        <v>0.3131191898750512</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-8.167273192660964e-07</v>
+        <v>-2.211151546177397e-06</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>0.3296643495559692</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.4074911415768804</v>
+        <v>0.3131158395202583</v>
       </c>
     </row>
     <row r="78">
@@ -62943,7 +62943,7 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>-3.128590021429696e-06</v>
+        <v>-3.752393347619798e-06</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>0.3475290834903717</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.407485697831874</v>
+        <v>0.3131104701932706</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>0.3527332842350006</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.4074797050984437</v>
+        <v>0.3131044774598403</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>0.3580147624015808</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.4074743373098653</v>
+        <v>0.3130991096712619</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>0.3570431470870972</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.407474374058357</v>
+        <v>0.3130991464197536</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>0.3704661726951599</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.4074744843038325</v>
+        <v>0.3130992566652291</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>0.3481540381908417</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.6267998384952288</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.4074745578008162</v>
+        <v>0.3130993301622127</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>0.4359592795372009</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.2923176106410809</v>
+        <v>0.3</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.4074747415432753</v>
+        <v>0.3130995139046719</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.5828226804733276</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.2923176106410809</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.4074762849799318</v>
+        <v>0.3131010573413284</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>0.4596897661685944</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.2923176106410809</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.4074777549196049</v>
+        <v>0.3131025272810015</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>0.4722340404987335</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.2923176106410809</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.4074790043683268</v>
+        <v>0.3131037767297234</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.9741583466529846</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.011435059777391</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.4074803640625242</v>
+        <v>0.3131051364239207</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.5793165564537048</v>
       </c>
       <c r="JB89" t="n">
-        <v>1.011435059777391</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.4074781591530149</v>
+        <v>0.3131029315144115</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>0.4903234243392944</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.2923176106410809</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.4074777549196049</v>
+        <v>0.3131025272810015</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>0.4513998925685883</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.4267998384952287</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.4074769097042929</v>
+        <v>0.3131016820656894</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>0.2931315004825592</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.4074774609316701</v>
+        <v>0.3131022332930667</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>0.2234224379062653</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.4074771301952437</v>
+        <v>0.3131019025566403</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>0.3121365308761597</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.4074768362073093</v>
+        <v>0.3131016085687058</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>0.2269098907709122</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.4074769097042929</v>
+        <v>0.3131016820656894</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>0.2185086905956268</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.407476468722391</v>
+        <v>0.3131012410837875</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>0.2572046220302582</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.4074763584769154</v>
+        <v>0.313101130838312</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>0.3206404447555542</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.4074763217284237</v>
+        <v>0.3131010940898203</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>0.3216778337955475</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.2923176106410809</v>
+        <v>0.16</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.407476468722391</v>
+        <v>0.3131012410837875</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.5663644671440125</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.011435059777391</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.4074759909919973</v>
+        <v>0.3131007633533939</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.7026200890541077</v>
       </c>
       <c r="JB101" t="n">
-        <v>1.011435059777391</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.4074769464527846</v>
+        <v>0.3131017188141811</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>0.3831514120101929</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.2923176106410809</v>
+        <v>0.16</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.4074769097042929</v>
+        <v>0.3131016820656894</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>0.3120499849319458</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.4267998384952287</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.4074765789678665</v>
+        <v>0.3131013513292631</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>0.3024279177188873</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.4074770199497684</v>
+        <v>0.313101792311165</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>0.2290897369384766</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.4074763952254073</v>
+        <v>0.3131011675868039</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>0.2312830090522766</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.4074762114829482</v>
+        <v>0.3131009838443448</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>0.2024768888950348</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.4074758072495381</v>
+        <v>0.3131005796109347</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>0.1859357506036758</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.4074749620342262</v>
+        <v>0.3130997343956227</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>0.2067436277866364</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.4074749252857345</v>
+        <v>0.313099697647131</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>0.2544684410095215</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.4074750722797017</v>
+        <v>0.3130998446410983</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>0.2965917885303497</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.6267998384952288</v>
+        <v>0.16</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.4074749987827181</v>
+        <v>0.3130997711441147</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>0.4196511507034302</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.6267998384952288</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.4074750722797017</v>
+        <v>0.3130998446410983</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>0.3951364755630493</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.6267998384952288</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.4074751090281936</v>
+        <v>0.3130998813895902</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>0.4925622045993805</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.6267998384952288</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.4074749987827181</v>
+        <v>0.3130997711441147</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>0.3824326992034912</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.6267998384952288</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.40747543976462</v>
+        <v>0.3131002121260166</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>0.4096616208553314</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.6267998384952288</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.4074753295191445</v>
+        <v>0.313100101880541</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>0.3761482834815979</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.6267998384952288</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.4074752927706526</v>
+        <v>0.3131000651320491</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>0.3424386084079742</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.6267998384952288</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.4074752192736689</v>
+        <v>0.3130999916350655</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>0.3364452421665192</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.3</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.4074751825251772</v>
+        <v>0.3130999548865738</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>0.3370780646800995</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.3</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.4074749620342262</v>
+        <v>0.3130997343956227</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>0.3483866751194</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.16</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.4074748885372426</v>
+        <v>0.3130996608986391</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>0.3680238723754883</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.4074748150402589</v>
+        <v>0.3130995874016555</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>0.3758509457111359</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.6267998384952288</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.4074748517887509</v>
+        <v>0.3130996241501474</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>0.4007492959499359</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.6267998384952288</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.4074747415432753</v>
+        <v>0.3130995139046719</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>0.4896222651004791</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.6267998384952288</v>
+        <v>1</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.4074748517887509</v>
+        <v>0.3130996241501474</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>0.4900925159454346</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.6267998384952288</v>
+        <v>1.14</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.4074751457766853</v>
+        <v>0.3130999181380819</v>
       </c>
     </row>
   </sheetData>
